--- a/output/Efficiency_Comparison_Results.xlsx
+++ b/output/Efficiency_Comparison_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_9418C5AB13C031BF906DD65209F166D47EE19334" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{97F3F700-281F-4400-884A-BC1F6A0D9430}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2DAAAC361F58D72EDF75816D4E94079D4FC06674" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84462B4C-3D0D-4C16-BF2F-CA2E6D0844B4}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="21" activeTab="23" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Set1_Summary" sheetId="1" r:id="rId1"/>
@@ -54,20 +54,7 @@
     <sheet name="Set2_S6_Binary_GENMOD_Efficienc" sheetId="39" r:id="rId39"/>
     <sheet name="Raw_SE_Comparisons" sheetId="40" r:id="rId40"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -607,16 +594,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
@@ -641,16 +628,16 @@
         <v>3</v>
       </c>
       <c r="B4">
+        <v>7</v>
+      </c>
+      <c r="C4">
+        <v>7</v>
+      </c>
+      <c r="D4">
+        <v>4</v>
+      </c>
+      <c r="E4">
         <v>5</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-      <c r="D4">
-        <v>0</v>
-      </c>
-      <c r="E4">
-        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
@@ -658,16 +645,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C5">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
@@ -675,10 +662,10 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="C6">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="D6">
         <v>7</v>
@@ -692,16 +679,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C7">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -743,19 +730,19 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -794,10 +781,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="C2">
         <v>7</v>
@@ -845,25 +832,25 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -896,16 +883,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
@@ -959,13 +946,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F2">
         <v>0</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2">
         <v>0</v>
@@ -1058,7 +1045,7 @@
         <v>7</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J2">
         <v>2.88009148930395E-2</v>
@@ -1076,7 +1063,7 @@
         <v>1.9096717978507101</v>
       </c>
       <c r="O2">
-        <v>0</v>
+        <v>0.71428571428571397</v>
       </c>
       <c r="P2" t="s">
         <v>34</v>
@@ -1108,7 +1095,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>0.16102354657946699</v>
@@ -1126,7 +1113,7 @@
         <v>2.0414766877482</v>
       </c>
       <c r="O3">
-        <v>0</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="P3" t="s">
         <v>34</v>
@@ -1158,7 +1145,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>-0.62780342287614499</v>
@@ -1176,7 +1163,7 @@
         <v>-9.3402468618504805E-2</v>
       </c>
       <c r="O4">
-        <v>0</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="P4" t="s">
         <v>34</v>
@@ -1208,7 +1195,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J5">
         <v>-0.37989049562705002</v>
@@ -1226,7 +1213,7 @@
         <v>-9.4994662671028296E-2</v>
       </c>
       <c r="O5">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P5" t="s">
         <v>34</v>
@@ -1458,7 +1445,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="J10">
         <v>11.462275411109999</v>
@@ -1476,7 +1463,7 @@
         <v>20.174980412640402</v>
       </c>
       <c r="O10">
-        <v>0.71428571428571397</v>
+        <v>1</v>
       </c>
       <c r="P10" t="s">
         <v>34</v>
@@ -1508,7 +1495,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J11">
         <v>10.0459614420056</v>
@@ -1526,7 +1513,7 @@
         <v>17.789664524055699</v>
       </c>
       <c r="O11">
-        <v>0.42857142857142899</v>
+        <v>1</v>
       </c>
       <c r="P11" t="s">
         <v>34</v>
@@ -1558,7 +1545,7 @@
         <v>7</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J12">
         <v>-0.94800529294950897</v>
@@ -1576,7 +1563,7 @@
         <v>1.31390334438573</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="P12" t="s">
         <v>34</v>
@@ -1608,7 +1595,7 @@
         <v>7</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J13">
         <v>-1.4265055178277499</v>
@@ -1626,7 +1613,7 @@
         <v>1.4441767968181001</v>
       </c>
       <c r="O13">
-        <v>0</v>
+        <v>0.71428571428571397</v>
       </c>
       <c r="P13" t="s">
         <v>34</v>
@@ -1658,7 +1645,7 @@
         <v>7</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>-1.63215453104813</v>
@@ -1676,7 +1663,7 @@
         <v>-0.75236095358942401</v>
       </c>
       <c r="O14">
-        <v>0</v>
+        <v>0.71428571428571397</v>
       </c>
       <c r="P14" t="s">
         <v>34</v>
@@ -1708,7 +1695,7 @@
         <v>7</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J15">
         <v>-1.4376168869799999</v>
@@ -1726,7 +1713,7 @@
         <v>-0.66546027669137897</v>
       </c>
       <c r="O15">
-        <v>0</v>
+        <v>0.71428571428571397</v>
       </c>
       <c r="P15" t="s">
         <v>34</v>
@@ -1758,7 +1745,7 @@
         <v>7</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J16">
         <v>-1.78200084236553</v>
@@ -1776,7 +1763,7 @@
         <v>-0.82731489938687397</v>
       </c>
       <c r="O16">
-        <v>0</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="P16" t="s">
         <v>34</v>
@@ -1808,7 +1795,7 @@
         <v>7</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J17">
         <v>-1.6880338282624101</v>
@@ -1826,7 +1813,7 @@
         <v>-1.0127763183927201</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P17" t="s">
         <v>34</v>
@@ -1858,7 +1845,7 @@
         <v>7</v>
       </c>
       <c r="I18">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J18">
         <v>-11.9202195612437</v>
@@ -1876,7 +1863,7 @@
         <v>-1.25012418452165</v>
       </c>
       <c r="O18">
-        <v>0.42857142857142899</v>
+        <v>1</v>
       </c>
       <c r="P18" t="s">
         <v>34</v>
@@ -1908,7 +1895,7 @@
         <v>7</v>
       </c>
       <c r="I19">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J19">
         <v>-11.1090605491706</v>
@@ -1926,7 +1913,7 @@
         <v>-0.74716453745677502</v>
       </c>
       <c r="O19">
-        <v>0.42857142857142899</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="P19" t="s">
         <v>34</v>
@@ -2058,7 +2045,7 @@
         <v>7</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J22">
         <v>-4.2245273750920704</v>
@@ -2076,7 +2063,7 @@
         <v>-3.38280980324474</v>
       </c>
       <c r="O22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P22" t="s">
         <v>34</v>
@@ -2108,7 +2095,7 @@
         <v>7</v>
       </c>
       <c r="I23">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J23">
         <v>-3.4844473588229401</v>
@@ -2126,7 +2113,7 @@
         <v>-3.15308275377041</v>
       </c>
       <c r="O23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P23" t="s">
         <v>34</v>
@@ -2158,7 +2145,7 @@
         <v>7</v>
       </c>
       <c r="I24">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J24">
         <v>-1.4350852606470299</v>
@@ -2176,7 +2163,7 @@
         <v>3.77456771753115E-4</v>
       </c>
       <c r="O24">
-        <v>0</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="P24" t="s">
         <v>34</v>
@@ -2208,7 +2195,7 @@
         <v>7</v>
       </c>
       <c r="I25">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J25">
         <v>-1.30846808136249</v>
@@ -2226,7 +2213,7 @@
         <v>-0.305793485963817</v>
       </c>
       <c r="O25">
-        <v>0</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="P25" t="s">
         <v>34</v>
@@ -2258,7 +2245,7 @@
         <v>7</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J26">
         <v>-0.48004226089218299</v>
@@ -2276,7 +2263,7 @@
         <v>3.7907505686122202E-2</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P26" t="s">
         <v>40</v>
@@ -2358,7 +2345,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J28">
         <v>-0.42158925709475498</v>
@@ -2376,7 +2363,7 @@
         <v>2.2243791959874502E-2</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P28" t="s">
         <v>40</v>
@@ -3058,7 +3045,7 @@
         <v>7</v>
       </c>
       <c r="I42">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J42">
         <v>-1.5889624997827301</v>
@@ -3076,7 +3063,7 @@
         <v>0.79935535858179396</v>
       </c>
       <c r="O42">
-        <v>0</v>
+        <v>0.42857142857142899</v>
       </c>
       <c r="P42" t="s">
         <v>40</v>
@@ -3108,7 +3095,7 @@
         <v>7</v>
       </c>
       <c r="I43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J43">
         <v>-1.0944712424517899</v>
@@ -3126,7 +3113,7 @@
         <v>-0.183642210442752</v>
       </c>
       <c r="O43">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P43" t="s">
         <v>42</v>
@@ -3158,7 +3145,7 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="J44">
         <v>-1.48525763273249</v>
@@ -3176,7 +3163,7 @@
         <v>0.82997621705576796</v>
       </c>
       <c r="O44">
-        <v>0</v>
+        <v>0.42857142857142899</v>
       </c>
       <c r="P44" t="s">
         <v>40</v>
@@ -3208,7 +3195,7 @@
         <v>7</v>
       </c>
       <c r="I45">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J45">
         <v>-1.04658583073335</v>
@@ -3226,7 +3213,7 @@
         <v>-0.16265155224351399</v>
       </c>
       <c r="O45">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P45" t="s">
         <v>42</v>
@@ -3258,7 +3245,7 @@
         <v>7</v>
       </c>
       <c r="I46">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="J46">
         <v>3.87715988053889</v>
@@ -3276,7 +3263,7 @@
         <v>9.7234891676168704</v>
       </c>
       <c r="O46">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P46" t="s">
         <v>40</v>
@@ -3308,7 +3295,7 @@
         <v>7</v>
       </c>
       <c r="I47">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J47">
         <v>0.52649545097238504</v>
@@ -3326,7 +3313,7 @@
         <v>1.37115165336375</v>
       </c>
       <c r="O47">
-        <v>0</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="P47" t="s">
         <v>42</v>
@@ -3358,7 +3345,7 @@
         <v>7</v>
       </c>
       <c r="I48">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="J48">
         <v>3.4551773001194399</v>
@@ -3376,7 +3363,7 @@
         <v>8.8223164840344008</v>
       </c>
       <c r="O48">
-        <v>0</v>
+        <v>0.85714285714285698</v>
       </c>
       <c r="P48" t="s">
         <v>40</v>
@@ -3408,7 +3395,7 @@
         <v>7</v>
       </c>
       <c r="I49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J49">
         <v>0.62400698458926995</v>
@@ -3426,7 +3413,7 @@
         <v>1.2548603746907101</v>
       </c>
       <c r="O49">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P49" t="s">
         <v>42</v>
@@ -3458,7 +3445,7 @@
         <v>7</v>
       </c>
       <c r="I50">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J50">
         <v>0.99740020425002796</v>
@@ -3476,7 +3463,7 @@
         <v>1.12223756906077</v>
       </c>
       <c r="O50">
-        <v>0</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="P50" t="s">
         <v>40</v>
@@ -3558,7 +3545,7 @@
         <v>7</v>
       </c>
       <c r="I52">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J52">
         <v>0.90086157388995203</v>
@@ -3576,7 +3563,7 @@
         <v>1.1245674740484399</v>
       </c>
       <c r="O52">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P52" t="s">
         <v>40</v>
@@ -3658,7 +3645,7 @@
         <v>7</v>
       </c>
       <c r="I54">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J54">
         <v>1.09485844114244</v>
@@ -3676,7 +3663,7 @@
         <v>1.41534645675259</v>
       </c>
       <c r="O54">
-        <v>0</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="P54" t="s">
         <v>40</v>
@@ -3858,7 +3845,7 @@
         <v>7</v>
       </c>
       <c r="I58">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J58">
         <v>-0.68065729608635805</v>
@@ -3876,7 +3863,7 @@
         <v>0.63137359226745104</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="P58" t="s">
         <v>40</v>
@@ -3958,7 +3945,7 @@
         <v>7</v>
       </c>
       <c r="I60">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J60">
         <v>-0.63787886030127305</v>
@@ -3976,7 +3963,7 @@
         <v>0.50190724754065097</v>
       </c>
       <c r="O60">
-        <v>0</v>
+        <v>0.28571428571428598</v>
       </c>
       <c r="P60" t="s">
         <v>40</v>
@@ -4058,7 +4045,7 @@
         <v>7</v>
       </c>
       <c r="I62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J62">
         <v>-0.198756128916113</v>
@@ -4076,7 +4063,7 @@
         <v>0.41643082396701903</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P62" t="s">
         <v>40</v>
@@ -4158,7 +4145,7 @@
         <v>7</v>
       </c>
       <c r="I64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J64">
         <v>-6.5561462627345704E-2</v>
@@ -4176,7 +4163,7 @@
         <v>1.0727662824102699</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P64" t="s">
         <v>40</v>
@@ -4458,7 +4445,7 @@
         <v>7</v>
       </c>
       <c r="I70">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J70">
         <v>1.05917528216023</v>
@@ -4476,7 +4463,7 @@
         <v>1.40835094329731</v>
       </c>
       <c r="O70">
-        <v>0</v>
+        <v>0.57142857142857095</v>
       </c>
       <c r="P70" t="s">
         <v>40</v>
@@ -4558,7 +4545,7 @@
         <v>7</v>
       </c>
       <c r="I72">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J72">
         <v>0.64343047219474503</v>
@@ -4576,7 +4563,7 @@
         <v>1.04330300246008</v>
       </c>
       <c r="O72">
-        <v>0</v>
+        <v>0.14285714285714299</v>
       </c>
       <c r="P72" t="s">
         <v>40</v>
@@ -4843,7 +4830,7 @@
         <v>-1.0382925855260301</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -4872,7 +4859,7 @@
         <v>-2.5015832805573002</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5075,7 +5062,7 @@
         <v>-1.29312778813033</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -5173,7 +5160,7 @@
         <v>1.9096717978507101</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -5231,7 +5218,7 @@
         <v>1.59395973154363</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -5260,7 +5247,7 @@
         <v>1.0017643599294199</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -5289,7 +5276,7 @@
         <v>-1.01343908349857</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -5318,7 +5305,7 @@
         <v>-4.5996592844974504</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -5376,7 +5363,7 @@
         <v>2.0414766877482</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -5434,7 +5421,7 @@
         <v>1.60658772158807</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -5463,7 +5450,7 @@
         <v>1.04553119730185</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -5521,7 +5508,7 @@
         <v>-4.0442741592166902</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6461,13 +6448,13 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
         <v>0</v>
@@ -6519,28 +6506,28 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="C4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F4">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H4">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6548,19 +6535,19 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C5">
         <v>0</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G5">
         <v>0</v>
@@ -6577,25 +6564,25 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I6">
         <v>0</v>
@@ -6618,13 +6605,13 @@
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G7">
         <v>0</v>
       </c>
       <c r="H7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -6725,7 +6712,7 @@
         <v>1.31390334438573</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -6754,7 +6741,7 @@
         <v>-2.63316078756979</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -6812,7 +6799,7 @@
         <v>-1.7679258829364899</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -6870,7 +6857,7 @@
         <v>-2.1828492810523401</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -6928,7 +6915,7 @@
         <v>1.4441767968181001</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -6957,7 +6944,7 @@
         <v>-3.24222201424173</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7015,7 +7002,7 @@
         <v>-2.4642781171179502</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -7044,7 +7031,7 @@
         <v>-1.6193503713962001</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -7073,7 +7060,7 @@
         <v>-3.7199704674100298</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -7200,7 +7187,7 @@
         <v>1.48415812409857</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -7258,7 +7245,7 @@
         <v>2.9186253752945701</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -7345,7 +7332,7 @@
         <v>9.7402999967526291</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -7403,7 +7390,7 @@
         <v>1.39240703041227</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7461,7 +7448,7 @@
         <v>2.7731505338973901</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -7490,7 +7477,7 @@
         <v>8.7262200165425892</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -7588,7 +7575,7 @@
         <v>-2.0975769455191</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -7617,7 +7604,7 @@
         <v>-1.2969075364312399</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -7646,7 +7633,7 @@
         <v>-2.0514578039320601</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -7675,7 +7662,7 @@
         <v>-2.0313319175026798</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -7733,7 +7720,7 @@
         <v>-2.5378938970881699</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -7762,7 +7749,7 @@
         <v>-1.6315228966986099</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -7791,7 +7778,7 @@
         <v>-1.62476375663298</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -7820,7 +7807,7 @@
         <v>-1.26240478750968</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -7849,7 +7836,7 @@
         <v>-2.2182274659718799</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -7878,7 +7865,7 @@
         <v>-1.5600106574446999</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -7907,7 +7894,7 @@
         <v>-1.0127763183927201</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -7936,7 +7923,7 @@
         <v>-2.4973960225758698</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -7965,7 +7952,7 @@
         <v>-1.64065778930902</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8034,7 +8021,7 @@
         <v>-1.8080966909990701</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -8092,7 +8079,7 @@
         <v>-2.0238412952584399</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -8121,7 +8108,7 @@
         <v>-1.4091989375087299</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -8179,7 +8166,7 @@
         <v>-1.79494543365882</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -8208,7 +8195,7 @@
         <v>-2.7413240011665301</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -8237,7 +8224,7 @@
         <v>-1.4686382973955201</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -8295,7 +8282,7 @@
         <v>-1.9122592242488099</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -8324,7 +8311,7 @@
         <v>-1.0940985447427101</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -8382,7 +8369,7 @@
         <v>-1.6681172033652401</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -8411,7 +8398,7 @@
         <v>-2.5453481568168499</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -8955,7 +8942,7 @@
         <v>-6.7552253219941498</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -8984,7 +8971,7 @@
         <v>-5.8763630977727503</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -9013,7 +9000,7 @@
         <v>-1.25012418452165</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -9042,7 +9029,7 @@
         <v>-3.2149682510325999</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -9158,7 +9145,7 @@
         <v>-5.7783990736200801</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -9187,7 +9174,7 @@
         <v>-5.5104819993478698</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -9245,7 +9232,7 @@
         <v>-2.7785301193302301</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -9372,7 +9359,7 @@
         <v>-1.83687513200837</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9401,7 +9388,7 @@
         <v>-1.5541271810574599</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -9430,7 +9417,7 @@
         <v>-1.59858112711128</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -9459,7 +9446,7 @@
         <v>-1.9610380443733499</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -9517,7 +9504,7 @@
         <v>-1.4543851917144099</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -9546,7 +9533,7 @@
         <v>-1.64096760503608</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -9575,7 +9562,7 @@
         <v>-1.3204410601149501</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -9604,7 +9591,7 @@
         <v>-1.41479099678458</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -9633,7 +9620,7 @@
         <v>-1.6625392450445</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -9662,7 +9649,7 @@
         <v>-1.41098651637018</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -9720,7 +9707,7 @@
         <v>-1.45483533456229</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -9749,7 +9736,7 @@
         <v>-1.5898899306971099</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -9818,7 +9805,7 @@
         <v>-4.4017682929398996</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9847,7 +9834,7 @@
         <v>-4.1139424699952203</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -9876,7 +9863,7 @@
         <v>-4.8902349627686297</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -9905,7 +9892,7 @@
         <v>-4.3954288959080099</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -9934,7 +9921,7 @@
         <v>-3.9639147074904302</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -9963,7 +9950,7 @@
         <v>-3.38280980324474</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -9992,7 +9979,7 @@
         <v>-4.4235924932975896</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -10021,7 +10008,7 @@
         <v>-3.2546290144471999</v>
       </c>
       <c r="I9">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.25">
@@ -10050,7 +10037,7 @@
         <v>-3.1710640406292501</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.25">
@@ -10079,7 +10066,7 @@
         <v>-4.1078720737476404</v>
       </c>
       <c r="I11">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.25">
@@ -10108,7 +10095,7 @@
         <v>-3.15308275377041</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -10137,7 +10124,7 @@
         <v>-3.2200499036669799</v>
       </c>
       <c r="I13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.25">
@@ -10166,7 +10153,7 @@
         <v>-3.4354374682687401</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -10195,7 +10182,7 @@
         <v>-4.0489962572303604</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -11290,7 +11277,7 @@
         <v>-1.48216767021769</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -11696,7 +11683,7 @@
         <v>-1.1405109489051</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -11929,16 +11916,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -13711,7 +13698,7 @@
         <v>3.3310286096557702</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -13740,7 +13727,7 @@
         <v>2.8820823417988399</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -13769,7 +13756,7 @@
         <v>1.3071840211663399</v>
       </c>
       <c r="I4">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.25">
@@ -13798,7 +13785,7 @@
         <v>1.5843468546288</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -13827,7 +13814,7 @@
         <v>1.3804394286835699</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
@@ -13856,7 +13843,7 @@
         <v>6.9315487402220404</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -13885,7 +13872,7 @@
         <v>9.7234891676168704</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -14059,7 +14046,7 @@
         <v>1.0969042923305401</v>
       </c>
       <c r="I14">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.25">
@@ -14088,7 +14075,7 @@
         <v>1.37115165336375</v>
       </c>
       <c r="I15">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.25">
@@ -14117,7 +14104,7 @@
         <v>2.4091747208882999</v>
       </c>
       <c r="I16">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.25">
@@ -14146,7 +14133,7 @@
         <v>2.38137174282038</v>
       </c>
       <c r="I17">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.25">
@@ -14175,7 +14162,7 @@
         <v>1.75036202843047</v>
       </c>
       <c r="I18">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.25">
@@ -14233,7 +14220,7 @@
         <v>1.7393790837180401</v>
       </c>
       <c r="I20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.25">
@@ -14262,7 +14249,7 @@
         <v>6.18156208823663</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -14291,7 +14278,7 @@
         <v>8.8223164840344008</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -14494,7 +14481,7 @@
         <v>1.2548603746907101</v>
       </c>
       <c r="I29">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -14650,7 +14637,7 @@
         <v>-4.08161073825503</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -14708,7 +14695,7 @@
         <v>-3.17546331418664</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -14737,7 +14724,7 @@
         <v>-4.9159838911262304</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -14853,7 +14840,7 @@
         <v>-3.9441610738255002</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.25">
@@ -15056,7 +15043,7 @@
         <v>-4.1602139156593001</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -15114,7 +15101,7 @@
         <v>-2.6755852842809298</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -15143,7 +15130,7 @@
         <v>-4.4223412394797297</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -15259,7 +15246,7 @@
         <v>-3.8137151133641498</v>
       </c>
       <c r="I26">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.25">
@@ -15415,7 +15402,7 @@
         <v>1.41534645675259</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -15444,7 +15431,7 @@
         <v>1.0676017609973401</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -15502,7 +15489,7 @@
         <v>1.37562678280493</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -15589,7 +15576,7 @@
         <v>1.07087712307616</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -16267,7 +16254,7 @@
         <v>1.0446381457573699</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -16354,7 +16341,7 @@
         <v>1.00933554763708</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -16412,7 +16399,7 @@
         <v>1.12223756906077</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.25">
@@ -16441,7 +16428,7 @@
         <v>1.0072941993747799</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -16818,7 +16805,7 @@
         <v>1.1245674740484399</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -17293,7 +17280,7 @@
         <v>-1.10252933199693</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -17670,7 +17657,7 @@
         <v>1.0727662824102699</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -18058,7 +18045,7 @@
         <v>-1.33806504159638</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -18145,7 +18132,7 @@
         <v>-4.3176561295296896</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -18464,7 +18451,7 @@
         <v>-1.3972343402749201</v>
       </c>
       <c r="I19">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.25">
@@ -18551,7 +18538,7 @@
         <v>-3.8386971694455299</v>
       </c>
       <c r="I22">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.25">
@@ -18823,7 +18810,7 @@
         <v>1.40835094329731</v>
       </c>
       <c r="I2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -18852,7 +18839,7 @@
         <v>1.0282063460448301</v>
       </c>
       <c r="I3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
@@ -18910,7 +18897,7 @@
         <v>1.35615869816062</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.25">
@@ -18997,7 +18984,7 @@
         <v>1.1105585943974801</v>
       </c>
       <c r="I8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.25">
@@ -19374,7 +19361,7 @@
         <v>1.04330300246008</v>
       </c>
       <c r="I21">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.25">
@@ -20500,13 +20487,13 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B2">
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2">
         <v>0</v>
@@ -20884,7 +20871,7 @@
         <v>-1.29312778813033</v>
       </c>
       <c r="G8">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" t="s">
         <v>28</v>
@@ -21307,7 +21294,7 @@
         <v>1.4441767968181001</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H17" t="s">
         <v>28</v>
@@ -21354,7 +21341,7 @@
         <v>-3.24222201424173</v>
       </c>
       <c r="G18">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H18" t="s">
         <v>28</v>
@@ -21448,7 +21435,7 @@
         <v>-2.4642781171179502</v>
       </c>
       <c r="G20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="s">
         <v>28</v>
@@ -21495,7 +21482,7 @@
         <v>-1.6193503713962001</v>
       </c>
       <c r="G21">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" t="s">
         <v>28</v>
@@ -21542,7 +21529,7 @@
         <v>-3.7199704674100298</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="s">
         <v>28</v>
@@ -21589,7 +21576,7 @@
         <v>-1.62476375663298</v>
       </c>
       <c r="G23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" t="s">
         <v>28</v>
@@ -21636,7 +21623,7 @@
         <v>-1.26240478750968</v>
       </c>
       <c r="G24">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H24" t="s">
         <v>28</v>
@@ -21683,7 +21670,7 @@
         <v>-2.2182274659718799</v>
       </c>
       <c r="G25">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H25" t="s">
         <v>28</v>
@@ -21730,7 +21717,7 @@
         <v>-1.5600106574446999</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H26" t="s">
         <v>28</v>
@@ -21777,7 +21764,7 @@
         <v>-1.0127763183927201</v>
       </c>
       <c r="G27">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" t="s">
         <v>28</v>
@@ -21824,7 +21811,7 @@
         <v>-2.4973960225758698</v>
       </c>
       <c r="G28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H28" t="s">
         <v>28</v>
@@ -21871,7 +21858,7 @@
         <v>-1.64065778930902</v>
       </c>
       <c r="G29">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" t="s">
         <v>28</v>
@@ -22247,7 +22234,7 @@
         <v>-1.3204410601149501</v>
       </c>
       <c r="G37">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H37" t="s">
         <v>28</v>
@@ -22294,7 +22281,7 @@
         <v>-1.41479099678458</v>
       </c>
       <c r="G38">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H38" t="s">
         <v>28</v>
@@ -22341,7 +22328,7 @@
         <v>-1.6625392450445</v>
       </c>
       <c r="G39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H39" t="s">
         <v>28</v>
@@ -22388,7 +22375,7 @@
         <v>-1.41098651637018</v>
       </c>
       <c r="G40">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H40" t="s">
         <v>28</v>
@@ -22482,7 +22469,7 @@
         <v>-1.45483533456229</v>
       </c>
       <c r="G42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H42" t="s">
         <v>28</v>
@@ -22529,7 +22516,7 @@
         <v>-1.5898899306971099</v>
       </c>
       <c r="G43">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H43" t="s">
         <v>28</v>
@@ -22811,7 +22798,7 @@
         <v>-1.0382925855260301</v>
       </c>
       <c r="G49">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H49" t="s">
         <v>28</v>
@@ -22858,7 +22845,7 @@
         <v>-2.5015832805573002</v>
       </c>
       <c r="G50">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H50" t="s">
         <v>28</v>
@@ -23281,7 +23268,7 @@
         <v>1.31390334438573</v>
       </c>
       <c r="G59">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H59" t="s">
         <v>28</v>
@@ -23328,7 +23315,7 @@
         <v>-2.63316078756979</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H60" t="s">
         <v>28</v>
@@ -23422,7 +23409,7 @@
         <v>-1.7679258829364899</v>
       </c>
       <c r="G62">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" t="s">
         <v>28</v>
@@ -23516,7 +23503,7 @@
         <v>-2.1828492810523401</v>
       </c>
       <c r="G64">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" t="s">
         <v>28</v>
@@ -23563,7 +23550,7 @@
         <v>-2.0975769455191</v>
       </c>
       <c r="G65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" t="s">
         <v>28</v>
@@ -23610,7 +23597,7 @@
         <v>-1.2969075364312399</v>
       </c>
       <c r="G66">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H66" t="s">
         <v>28</v>
@@ -23657,7 +23644,7 @@
         <v>-2.0514578039320601</v>
       </c>
       <c r="G67">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H67" t="s">
         <v>28</v>
@@ -23704,7 +23691,7 @@
         <v>-2.0313319175026798</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" t="s">
         <v>28</v>
@@ -23798,7 +23785,7 @@
         <v>-2.5378938970881699</v>
       </c>
       <c r="G70">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H70" t="s">
         <v>28</v>
@@ -23845,7 +23832,7 @@
         <v>-1.6315228966986099</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H71" t="s">
         <v>28</v>
@@ -24221,7 +24208,7 @@
         <v>-1.83687513200837</v>
       </c>
       <c r="G79">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H79" t="s">
         <v>28</v>
@@ -24268,7 +24255,7 @@
         <v>-1.5541271810574599</v>
       </c>
       <c r="G80">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H80" t="s">
         <v>28</v>
@@ -24315,7 +24302,7 @@
         <v>-1.59858112711128</v>
       </c>
       <c r="G81">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H81" t="s">
         <v>28</v>
@@ -24362,7 +24349,7 @@
         <v>-1.9610380443733499</v>
       </c>
       <c r="G82">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H82" t="s">
         <v>28</v>
@@ -24456,7 +24443,7 @@
         <v>-1.4543851917144099</v>
       </c>
       <c r="G84">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H84" t="s">
         <v>28</v>
@@ -24503,7 +24490,7 @@
         <v>-1.64096760503608</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H85" t="s">
         <v>28</v>
@@ -24597,7 +24584,7 @@
         <v>2.0414766877482</v>
       </c>
       <c r="G87">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H87" t="s">
         <v>28</v>
@@ -24691,7 +24678,7 @@
         <v>1.60658772158807</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H89" t="s">
         <v>28</v>
@@ -24738,7 +24725,7 @@
         <v>1.04553119730185</v>
       </c>
       <c r="G90">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H90" t="s">
         <v>28</v>
@@ -24832,7 +24819,7 @@
         <v>-4.0442741592166902</v>
       </c>
       <c r="G92">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H92" t="s">
         <v>28</v>
@@ -25208,7 +25195,7 @@
         <v>9.7402999967526291</v>
       </c>
       <c r="G100">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H100" t="s">
         <v>28</v>
@@ -25302,7 +25289,7 @@
         <v>1.39240703041227</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H102" t="s">
         <v>28</v>
@@ -25396,7 +25383,7 @@
         <v>2.7731505338973901</v>
       </c>
       <c r="G104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H104" t="s">
         <v>28</v>
@@ -25443,7 +25430,7 @@
         <v>8.7262200165425892</v>
       </c>
       <c r="G105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="s">
         <v>28</v>
@@ -25537,7 +25524,7 @@
         <v>-1.4686382973955201</v>
       </c>
       <c r="G107">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H107" t="s">
         <v>28</v>
@@ -25631,7 +25618,7 @@
         <v>-1.9122592242488099</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109" t="s">
         <v>28</v>
@@ -25678,7 +25665,7 @@
         <v>-1.0940985447427101</v>
       </c>
       <c r="G110">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H110" t="s">
         <v>28</v>
@@ -25772,7 +25759,7 @@
         <v>-1.6681172033652401</v>
       </c>
       <c r="G112">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H112" t="s">
         <v>28</v>
@@ -25819,7 +25806,7 @@
         <v>-2.5453481568168499</v>
       </c>
       <c r="G113">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H113" t="s">
         <v>28</v>
@@ -25913,7 +25900,7 @@
         <v>-5.7783990736200801</v>
       </c>
       <c r="G115">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H115" t="s">
         <v>28</v>
@@ -25960,7 +25947,7 @@
         <v>-5.5104819993478698</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116" t="s">
         <v>28</v>
@@ -26054,7 +26041,7 @@
         <v>-2.7785301193302301</v>
       </c>
       <c r="G118">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H118" t="s">
         <v>28</v>
@@ -26195,7 +26182,7 @@
         <v>-3.2546290144471999</v>
       </c>
       <c r="G121">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H121" t="s">
         <v>28</v>
@@ -26242,7 +26229,7 @@
         <v>-3.1710640406292501</v>
       </c>
       <c r="G122">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H122" t="s">
         <v>28</v>
@@ -26289,7 +26276,7 @@
         <v>-4.1078720737476404</v>
       </c>
       <c r="G123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H123" t="s">
         <v>28</v>
@@ -26336,7 +26323,7 @@
         <v>-3.15308275377041</v>
       </c>
       <c r="G124">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H124" t="s">
         <v>28</v>
@@ -26383,7 +26370,7 @@
         <v>-3.2200499036669799</v>
       </c>
       <c r="G125">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H125" t="s">
         <v>28</v>
@@ -26430,7 +26417,7 @@
         <v>-3.4354374682687401</v>
       </c>
       <c r="G126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H126" t="s">
         <v>28</v>
@@ -26477,7 +26464,7 @@
         <v>-4.0489962572303604</v>
       </c>
       <c r="G127">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H127" t="s">
         <v>28</v>
@@ -26571,7 +26558,7 @@
         <v>1.9096717978507101</v>
       </c>
       <c r="G129">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H129" t="s">
         <v>28</v>
@@ -26665,7 +26652,7 @@
         <v>1.59395973154363</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H131" t="s">
         <v>28</v>
@@ -26712,7 +26699,7 @@
         <v>1.0017643599294199</v>
       </c>
       <c r="G132">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H132" t="s">
         <v>28</v>
@@ -26759,7 +26746,7 @@
         <v>-1.01343908349857</v>
       </c>
       <c r="G133">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H133" t="s">
         <v>28</v>
@@ -26806,7 +26793,7 @@
         <v>-4.5996592844974504</v>
       </c>
       <c r="G134">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H134" t="s">
         <v>28</v>
@@ -27276,7 +27263,7 @@
         <v>1.48415812409857</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H144" t="s">
         <v>28</v>
@@ -27370,7 +27357,7 @@
         <v>2.9186253752945701</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H146" t="s">
         <v>28</v>
@@ -27511,7 +27498,7 @@
         <v>-1.8080966909990701</v>
       </c>
       <c r="G149">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H149" t="s">
         <v>28</v>
@@ -27605,7 +27592,7 @@
         <v>-2.0238412952584399</v>
       </c>
       <c r="G151">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H151" t="s">
         <v>28</v>
@@ -27652,7 +27639,7 @@
         <v>-1.4091989375087299</v>
       </c>
       <c r="G152">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H152" t="s">
         <v>28</v>
@@ -27746,7 +27733,7 @@
         <v>-1.79494543365882</v>
       </c>
       <c r="G154">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H154" t="s">
         <v>28</v>
@@ -27793,7 +27780,7 @@
         <v>-2.7413240011665301</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H155" t="s">
         <v>28</v>
@@ -27887,7 +27874,7 @@
         <v>-6.7552253219941498</v>
       </c>
       <c r="G157">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H157" t="s">
         <v>28</v>
@@ -27934,7 +27921,7 @@
         <v>-5.8763630977727503</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" t="s">
         <v>28</v>
@@ -27981,7 +27968,7 @@
         <v>-1.25012418452165</v>
       </c>
       <c r="G159">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H159" t="s">
         <v>28</v>
@@ -28028,7 +28015,7 @@
         <v>-3.2149682510325999</v>
       </c>
       <c r="G160">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H160" t="s">
         <v>28</v>
@@ -28169,7 +28156,7 @@
         <v>-4.4017682929398996</v>
       </c>
       <c r="G163">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H163" t="s">
         <v>28</v>
@@ -28216,7 +28203,7 @@
         <v>-4.1139424699952203</v>
       </c>
       <c r="G164">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H164" t="s">
         <v>28</v>
@@ -28263,7 +28250,7 @@
         <v>-4.8902349627686297</v>
       </c>
       <c r="G165">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H165" t="s">
         <v>28</v>
@@ -28310,7 +28297,7 @@
         <v>-4.3954288959080099</v>
       </c>
       <c r="G166">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H166" t="s">
         <v>28</v>
@@ -28357,7 +28344,7 @@
         <v>-3.9639147074904302</v>
       </c>
       <c r="G167">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H167" t="s">
         <v>28</v>
@@ -28404,7 +28391,7 @@
         <v>-3.38280980324474</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H168" t="s">
         <v>28</v>
@@ -28451,7 +28438,7 @@
         <v>-4.4235924932975896</v>
       </c>
       <c r="G169">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H169" t="s">
         <v>28</v>
@@ -29438,7 +29425,7 @@
         <v>1.2548603746907101</v>
       </c>
       <c r="G190">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H190" t="s">
         <v>37</v>
@@ -31130,7 +31117,7 @@
         <v>2.4091747208882999</v>
       </c>
       <c r="G226">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H226" t="s">
         <v>37</v>
@@ -31177,7 +31164,7 @@
         <v>2.38137174282038</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H227" t="s">
         <v>37</v>
@@ -31224,7 +31211,7 @@
         <v>1.75036202843047</v>
       </c>
       <c r="G228">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H228" t="s">
         <v>37</v>
@@ -31318,7 +31305,7 @@
         <v>1.7393790837180401</v>
       </c>
       <c r="G230">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H230" t="s">
         <v>37</v>
@@ -31365,7 +31352,7 @@
         <v>6.18156208823663</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H231" t="s">
         <v>37</v>
@@ -31412,7 +31399,7 @@
         <v>8.8223164840344008</v>
       </c>
       <c r="G232">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H232" t="s">
         <v>37</v>
@@ -32023,7 +32010,7 @@
         <v>1.0727662824102699</v>
       </c>
       <c r="G245">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H245" t="s">
         <v>37</v>
@@ -32352,7 +32339,7 @@
         <v>1.04330300246008</v>
       </c>
       <c r="G252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H252" t="s">
         <v>37</v>
@@ -33339,7 +33326,7 @@
         <v>1.0969042923305401</v>
       </c>
       <c r="G273">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H273" t="s">
         <v>37</v>
@@ -33386,7 +33373,7 @@
         <v>1.37115165336375</v>
       </c>
       <c r="G274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" t="s">
         <v>37</v>
@@ -35078,7 +35065,7 @@
         <v>3.3310286096557702</v>
       </c>
       <c r="G310">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H310" t="s">
         <v>37</v>
@@ -35125,7 +35112,7 @@
         <v>2.8820823417988399</v>
       </c>
       <c r="G311">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H311" t="s">
         <v>37</v>
@@ -35172,7 +35159,7 @@
         <v>1.3071840211663399</v>
       </c>
       <c r="G312">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" t="s">
         <v>37</v>
@@ -35219,7 +35206,7 @@
         <v>1.5843468546288</v>
       </c>
       <c r="G313">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H313" t="s">
         <v>37</v>
@@ -35266,7 +35253,7 @@
         <v>1.3804394286835699</v>
       </c>
       <c r="G314">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H314" t="s">
         <v>37</v>
@@ -35313,7 +35300,7 @@
         <v>6.9315487402220404</v>
       </c>
       <c r="G315">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H315" t="s">
         <v>37</v>
@@ -35360,7 +35347,7 @@
         <v>9.7234891676168704</v>
       </c>
       <c r="G316">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H316" t="s">
         <v>37</v>
@@ -35407,7 +35394,7 @@
         <v>1.41534645675259</v>
       </c>
       <c r="G317">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H317" t="s">
         <v>37</v>
@@ -35454,7 +35441,7 @@
         <v>1.0676017609973401</v>
       </c>
       <c r="G318">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" t="s">
         <v>37</v>
@@ -35548,7 +35535,7 @@
         <v>1.37562678280493</v>
       </c>
       <c r="G320">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H320" t="s">
         <v>37</v>
@@ -35689,7 +35676,7 @@
         <v>1.07087712307616</v>
       </c>
       <c r="G323">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H323" t="s">
         <v>37</v>
@@ -36018,7 +36005,7 @@
         <v>-1.10252933199693</v>
       </c>
       <c r="G330">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H330" t="s">
         <v>37</v>
@@ -36065,7 +36052,7 @@
         <v>1.40835094329731</v>
       </c>
       <c r="G331">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H331" t="s">
         <v>37</v>
@@ -36112,7 +36099,7 @@
         <v>1.0282063460448301</v>
       </c>
       <c r="G332">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H332" t="s">
         <v>37</v>
@@ -36206,7 +36193,7 @@
         <v>1.35615869816062</v>
       </c>
       <c r="G334">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H334" t="s">
         <v>37</v>
@@ -36347,7 +36334,7 @@
         <v>1.1105585943974801</v>
       </c>
       <c r="G337">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H337" t="s">
         <v>37</v>
@@ -37193,7 +37180,7 @@
         <v>-3.8137151133641498</v>
       </c>
       <c r="G355">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H355" t="s">
         <v>37</v>
@@ -38650,7 +38637,7 @@
         <v>-1.1405109489051</v>
       </c>
       <c r="G386">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H386" t="s">
         <v>37</v>
@@ -39167,7 +39154,7 @@
         <v>-4.1602139156593001</v>
       </c>
       <c r="G397">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" t="s">
         <v>37</v>
@@ -39261,7 +39248,7 @@
         <v>-2.6755852842809298</v>
       </c>
       <c r="G399">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H399" t="s">
         <v>37</v>
@@ -39308,7 +39295,7 @@
         <v>-4.4223412394797297</v>
       </c>
       <c r="G400">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H400" t="s">
         <v>37</v>
@@ -39590,7 +39577,7 @@
         <v>1.1245674740484399</v>
       </c>
       <c r="G406">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H406" t="s">
         <v>37</v>
@@ -39825,7 +39812,7 @@
         <v>-1.3972343402749201</v>
       </c>
       <c r="G411">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H411" t="s">
         <v>37</v>
@@ -39966,7 +39953,7 @@
         <v>-3.8386971694455299</v>
       </c>
       <c r="G414">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H414" t="s">
         <v>37</v>
@@ -41141,7 +41128,7 @@
         <v>-3.9441610738255002</v>
       </c>
       <c r="G439">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H439" t="s">
         <v>37</v>
@@ -42598,7 +42585,7 @@
         <v>-1.48216767021769</v>
       </c>
       <c r="G470">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H470" t="s">
         <v>37</v>
@@ -43115,7 +43102,7 @@
         <v>-4.08161073825503</v>
       </c>
       <c r="G481">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H481" t="s">
         <v>37</v>
@@ -43209,7 +43196,7 @@
         <v>-3.17546331418664</v>
       </c>
       <c r="G483">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H483" t="s">
         <v>37</v>
@@ -43256,7 +43243,7 @@
         <v>-4.9159838911262304</v>
       </c>
       <c r="G484">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H484" t="s">
         <v>37</v>
@@ -43303,7 +43290,7 @@
         <v>1.0446381457573699</v>
       </c>
       <c r="G485">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H485" t="s">
         <v>37</v>
@@ -43444,7 +43431,7 @@
         <v>1.00933554763708</v>
       </c>
       <c r="G488">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H488" t="s">
         <v>37</v>
@@ -43538,7 +43525,7 @@
         <v>1.12223756906077</v>
       </c>
       <c r="G490">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H490" t="s">
         <v>37</v>
@@ -43585,7 +43572,7 @@
         <v>1.0072941993747799</v>
       </c>
       <c r="G491">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H491" t="s">
         <v>37</v>
@@ -43773,7 +43760,7 @@
         <v>-1.33806504159638</v>
       </c>
       <c r="G495">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H495" t="s">
         <v>37</v>
@@ -43914,7 +43901,7 @@
         <v>-4.3176561295296896</v>
       </c>
       <c r="G498">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H498" t="s">
         <v>37</v>
@@ -44399,16 +44386,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+      <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>5</v>
-      </c>
-      <c r="B2">
-        <v>3</v>
-      </c>
-      <c r="C2">
-        <v>0</v>
-      </c>
-      <c r="D2">
-        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -44450,28 +44437,28 @@
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -44501,16 +44488,16 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="B2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="C2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>

--- a/output/Efficiency_Comparison_Results.xlsx
+++ b/output/Efficiency_Comparison_Results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2" documentId="11_2DAAAC361F58D72EDF75816D4E94079D4FC06674" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84462B4C-3D0D-4C16-BF2F-CA2E6D0844B4}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="11_2DAAAC361F58D72EDF75816D4E94079D4FC06674" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{AFCAAC9E-C285-4E33-BF44-DD5099EFE781}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31605" yWindow="2280" windowWidth="21600" windowHeight="11295" firstSheet="15" activeTab="15" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Set1_Summary" sheetId="1" r:id="rId1"/>
@@ -969,53 +969,53 @@
   <dimension ref="A1:P73"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="45" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>13</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="N1" t="s">
+      <c r="N1" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="O1" t="s">
+      <c r="O1" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="P1" t="s">
+      <c r="P1" s="1" t="s">
         <v>27</v>
       </c>
     </row>
@@ -4629,6 +4629,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0F00-000000000000}">
   <dimension ref="A1:I15"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="8" max="8" width="25.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
